--- a/public/sample-data/04-revenue-detail-FY2026-27-P2-August.xlsx
+++ b/public/sample-data/04-revenue-detail-FY2026-27-P2-August.xlsx
@@ -507,10 +507,10 @@
         <v>120000000</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>7881073.2</v>
       </c>
       <c r="G2">
-        <v>20000000</v>
+        <v>14073345</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -530,10 +530,10 @@
         <v>15000000</v>
       </c>
       <c r="F3">
-        <v>1250000</v>
+        <v>965232.45</v>
       </c>
       <c r="G3">
-        <v>2500000</v>
+        <v>1723629.38</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -553,10 +553,10 @@
         <v>60000000</v>
       </c>
       <c r="F4">
-        <v>5000000</v>
+        <v>3900733.2</v>
       </c>
       <c r="G4">
-        <v>10000000</v>
+        <v>6965595</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -576,10 +576,10 @@
         <v>2400000</v>
       </c>
       <c r="F5">
-        <v>180000</v>
+        <v>121002.34</v>
       </c>
       <c r="G5">
-        <v>360000</v>
+        <v>216075.6</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>6500000</v>
       </c>
       <c r="F6">
-        <v>210000</v>
+        <v>401019.26</v>
       </c>
       <c r="G6">
-        <v>420000</v>
+        <v>716105.81</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -645,10 +645,10 @@
         <v>4000000</v>
       </c>
       <c r="F8">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>4000000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
